--- a/ai_logs/Phan_Hoang_Nam_AILogs.xlsx
+++ b/ai_logs/Phan_Hoang_Nam_AILogs.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9708" activeTab="2"/>
+    <workbookView windowWidth="21000" windowHeight="9120" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="178">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -303,6 +303,54 @@
     <t>Hình mẫu Use Case Diagram [Image 2] từ ảnh do người dùng cung cấp</t>
   </si>
   <si>
+    <t>004</t>
+  </si>
+  <si>
+    <t>Code Generation + Algorithm Design + Reflection</t>
+  </si>
+  <si>
+    <t>Core logic: Data Generator và Query trong module lịch sử trình duyệt</t>
+  </si>
+  <si>
+    <t>Cần sinh dữ liệu hàng loạt để demo/test tải, không nhập tay; cần truy vấn theo title; cần đảm bảo timestamp tăng tuyến tính, không lỗi con trỏ khi thao tác danh sách liên kết</t>
+  </si>
+  <si>
+    <t>“Triển khai generateDummyData(numberOfPages), searchByTitle(keyword), viết flowchart và phản biện rủi ro AI trong khởi tạo dữ liệu.”</t>
+  </si>
+  <si>
+    <t>AI đề xuất thêm hàm sinh dữ liệu mẫu từ tập URL/Title phổ biến, timestamp tăng theo từng bước; bổ sung hàm tìm kiếm title theo từ khóa; mô tả flow thuật toán và cảnh báo rủi ro dữ liệu ngẫu nhiên thiếu kiểm soát</t>
+  </si>
+  <si>
+    <t>Human delta: hiệu chỉnh để đồng bộ với menu chạy thực tế, kiểm tra tính liên tục thời gian, tránh sai lệch khi duyệt/branch; xác nhận logic phải chạy được end-to-end thay vì chỉ có mô tả</t>
+  </si>
+  <si>
+    <t>Bản mô tả yêu cầu của GV; kết quả chạy chức năng Generate Data và Search Title trong bản simulator sau khi khôi phục; lịch sử trao đổi cho thấy đã từng mất menu và được thêm lại</t>
+  </si>
+  <si>
+    <t>005</t>
+  </si>
+  <si>
+    <t>Diagram Generation + Environment Adaptation</t>
+  </si>
+  <si>
+    <t>Visualization: xuất PNG flowchart trong thư mục diagrams theo cấu trúc mẫu có sẵn</t>
+  </si>
+  <si>
+    <t>Yêu cầu tạo 2 ảnh PNG theo style chuẩn của flowchart mẫu; rào cản công cụ render trên môi trường local</t>
+  </si>
+  <si>
+    <t>“Tiếp tục vẽ flowchart, lưu PNG trong diagrams, theo cấu trúc như flowchart mẫu, gồm Data Generator và searchByTitle.”</t>
+  </si>
+  <si>
+    <t>AI tạo script vẽ và xuất được 2 ảnh flowchart; khi Graphviz executable không khả dụng thì chuyển hướng render bằng phương án thay thế để vẫn tạo PNG đúng yêu cầu</t>
+  </si>
+  <si>
+    <t>Human delta: xác nhận đầu ra phải là file PNG thực tế trong đúng thư mục, không chỉ code; chấp nhận giải pháp fallback do giới hạn môi trường; giữ bố cục gần style mẫu để đồng nhất tài liệu nhóm</t>
+  </si>
+  <si>
+    <t>Có 2 file PNG đầu ra trong thư mục diagrams, tên tương ứng Data Generator và SearchByTitle; log lỗi ban đầu cho thấy thiếu Graphviz executable và log sau đó xác nhận ảnh đã được tạo</t>
+  </si>
+  <si>
     <t>HALLUCINATION DETECTION LOG (BẮT BUỘC)</t>
   </si>
   <si>
@@ -367,6 +415,36 @@
   </si>
   <si>
     <t>Cải tiến: AI nên đề xuất "Bạn có thể cần điều chỉnh vị trí các use case manually để khớp với ảnh mẫu chính xác."</t>
+  </si>
+  <si>
+    <t>Requirement Drift / Partial Completion</t>
+  </si>
+  <si>
+    <t>AI từng báo đã hoàn tất phần module, nhưng ở một thời điểm menu trong BrowserSimulator bị mất lại mục Generate Data và Search Title.</t>
+  </si>
+  <si>
+    <t>Chức năng trong BrowserHistory có (generateDummyData, searchByTitle) nhưng UI menu/handler phía simulator chưa luôn đồng bộ sau các lần chỉnh sửa.</t>
+  </si>
+  <si>
+    <t>Đối chiếu lại source và chạy luồng menu thấy chỉ còn lựa chọn 0-4, thiếu case 5-6.</t>
+  </si>
+  <si>
+    <t>Khôi phục đầy đủ case 5 và 6, thêm lại handleGenerateDummyData() và handleSearchByTitle(), kiểm tra lại prompt/flow để tránh mất tính năng khi refactor.</t>
+  </si>
+  <si>
+    <t>Tooling/Environment Hallucination (Execution Assumption)</t>
+  </si>
+  <si>
+    <t>AI ban đầu triển khai vẽ flowchart bằng Graphviz như thể có thể render PNG ngay.</t>
+  </si>
+  <si>
+    <t>Môi trường thiếu Graphviz executable (dot), nên script Graphviz không render được ảnh trực tiếp.</t>
+  </si>
+  <si>
+    <t>Log lỗi runtime báo ExecutableNotFound: failed to execute 'dot'.</t>
+  </si>
+  <si>
+    <t>Chuyển sang phương án thay thế khả thi (matplotlib), tạo thành công 2 file PNG trong diagrams; đồng thời cung cấp mã Graphviz riêng để dùng khi máy đã cài dot.</t>
   </si>
   <si>
     <t>HALLUCINATION TYPES REFERENCE:</t>
@@ -536,7 +614,7 @@
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="38">
+  <fonts count="37">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -656,13 +734,6 @@
       <color rgb="FF666666"/>
       <name val="Times New Roman"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1160,148 +1231,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1384,6 +1455,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2048,7 +2122,7 @@
       <c r="F4" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="G4" s="21" t="s">
+      <c r="G4" s="20" t="s">
         <v>61</v>
       </c>
       <c r="H4" s="20" t="s">
@@ -2074,7 +2148,7 @@
       <c r="F5" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="G5" s="21" t="s">
+      <c r="G5" s="20" t="s">
         <v>68</v>
       </c>
       <c r="H5" s="20" t="s">
@@ -2100,7 +2174,7 @@
       <c r="F6" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="G6" s="21" t="s">
+      <c r="G6" s="20" t="s">
         <v>76</v>
       </c>
       <c r="H6" s="26" t="s">
@@ -2108,26 +2182,56 @@
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="80" customHeight="1" spans="1:8">
-      <c r="A7" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15"/>
+      <c r="A7" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="G7" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="H7" s="15" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="80" customHeight="1" spans="1:8">
-      <c r="A8" s="15"/>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
+      <c r="A8" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="G8" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="H8" s="15" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="80" customHeight="1" spans="1:8">
       <c r="A9" s="15"/>
@@ -2323,32 +2427,32 @@
   <sheetData>
     <row r="1" ht="21" spans="1:6">
       <c r="A1" s="16" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="17" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" ht="40" customHeight="1" spans="1:6">
       <c r="A3" s="18" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="E3" s="18" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="F3" s="18" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" ht="60" customHeight="1" spans="1:6">
@@ -2356,19 +2460,19 @@
         <v>55</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="E4" s="21" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" ht="100.8" spans="1:6">
@@ -2376,19 +2480,19 @@
         <v>63</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="E5" s="22" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="F5" s="22" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1" spans="1:6">
@@ -2396,36 +2500,60 @@
         <v>70</v>
       </c>
       <c r="B6" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>113</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1" spans="1:6">
+      <c r="A7" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="F7" s="22" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1" spans="1:6">
+      <c r="A8" s="33" t="s">
         <v>86</v>
       </c>
-      <c r="C6" s="22" t="s">
-        <v>96</v>
-      </c>
-      <c r="D6" s="22" t="s">
-        <v>97</v>
-      </c>
-      <c r="E6" s="22" t="s">
-        <v>98</v>
-      </c>
-      <c r="F6" s="22" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="7" ht="60" customHeight="1" spans="1:6">
-      <c r="A7" s="22"/>
-      <c r="B7" s="22"/>
-      <c r="C7" s="22"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
-      <c r="F7" s="22"/>
-    </row>
-    <row r="8" ht="60" customHeight="1" spans="1:6">
-      <c r="A8" s="22"/>
-      <c r="B8" s="22"/>
-      <c r="C8" s="22"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22"/>
+      <c r="B8" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>122</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>124</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="9" ht="60" customHeight="1" spans="1:6">
       <c r="A9" s="22"/>
@@ -2557,73 +2685,73 @@
     </row>
     <row r="30" ht="18" spans="1:6">
       <c r="A30" s="23" t="s">
-        <v>100</v>
+        <v>126</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="24" t="s">
-        <v>101</v>
+        <v>127</v>
       </c>
       <c r="B31" s="24" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="C31" s="24" t="s">
-        <v>103</v>
+        <v>129</v>
       </c>
     </row>
     <row r="32" ht="28.8" spans="1:6">
       <c r="A32" s="22" t="s">
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="B32" s="22" t="s">
-        <v>105</v>
+        <v>131</v>
       </c>
       <c r="C32" s="22" t="s">
-        <v>106</v>
+        <v>132</v>
       </c>
     </row>
     <row r="33" ht="28.8" spans="1:3">
       <c r="A33" s="22" t="s">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="B33" s="22" t="s">
-        <v>108</v>
+        <v>134</v>
       </c>
       <c r="C33" s="22" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
     </row>
     <row r="34" ht="28.8" spans="1:3">
       <c r="A34" s="22" t="s">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="B34" s="22" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="C34" s="22" t="s">
-        <v>112</v>
+        <v>138</v>
       </c>
     </row>
     <row r="35" ht="28.8" spans="1:3">
       <c r="A35" s="22" t="s">
-        <v>113</v>
+        <v>139</v>
       </c>
       <c r="B35" s="22" t="s">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="C35" s="22" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
     </row>
     <row r="36" ht="43.2" spans="1:3">
       <c r="A36" s="22" t="s">
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="B36" s="22" t="s">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="C36" s="22" t="s">
-        <v>118</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -2651,195 +2779,195 @@
   <sheetData>
     <row r="1" ht="20.4" spans="1:4">
       <c r="A1" s="2" t="s">
-        <v>119</v>
+        <v>145</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>120</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" ht="17.4" spans="1:4">
       <c r="A4" s="4" t="s">
-        <v>121</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="5" t="s">
-        <v>122</v>
+        <v>148</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>125</v>
+        <v>151</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="7" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="D6" s="8"/>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="7" t="s">
-        <v>129</v>
+        <v>155</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>130</v>
+        <v>156</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="D7" s="8"/>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="7" t="s">
-        <v>131</v>
+        <v>157</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>132</v>
+        <v>158</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="D8" s="8"/>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="7" t="s">
-        <v>133</v>
+        <v>159</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>134</v>
+        <v>160</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="D9" s="8"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="7" t="s">
-        <v>135</v>
+        <v>161</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>136</v>
+        <v>162</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="D10" s="8"/>
     </row>
     <row r="12" ht="17.4" spans="1:4">
       <c r="A12" s="4" t="s">
-        <v>137</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="5" t="s">
-        <v>122</v>
+        <v>148</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>138</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="7" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>139</v>
+        <v>165</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="D14" s="8"/>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="7" t="s">
-        <v>129</v>
+        <v>155</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>140</v>
+        <v>166</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="D15" s="8"/>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="7" t="s">
-        <v>131</v>
+        <v>157</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>141</v>
+        <v>167</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="D16" s="8"/>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="7" t="s">
-        <v>133</v>
+        <v>159</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="D17" s="8"/>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="7" t="s">
-        <v>135</v>
+        <v>161</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="D18" s="8"/>
     </row>
     <row r="20" ht="15.6" spans="1:4">
       <c r="A20" s="9" t="s">
-        <v>144</v>
+        <v>170</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="10" t="s">
-        <v>145</v>
+        <v>171</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="10" t="s">
-        <v>146</v>
+        <v>172</v>
       </c>
     </row>
     <row r="25" ht="17.4" spans="1:4">
       <c r="A25" s="4" t="s">
-        <v>147</v>
+        <v>173</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="11" t="s">
-        <v>148</v>
+        <v>174</v>
       </c>
     </row>
     <row r="27" ht="41.4" spans="1:4">
@@ -2847,13 +2975,13 @@
         <v>47</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>149</v>
+        <v>175</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>150</v>
+        <v>176</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>151</v>
+        <v>177</v>
       </c>
     </row>
     <row r="28" spans="1:4">

--- a/ai_logs/Phan_Hoang_Nam_AILogs.xlsx
+++ b/ai_logs/Phan_Hoang_Nam_AILogs.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21000" windowHeight="9120" activeTab="1"/>
+    <workbookView windowWidth="21000" windowHeight="9180" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -531,7 +531,7 @@
     <t>Prompt này ảnh hưởng đến quyết định quan trọng trong project?</t>
   </si>
   <si>
-    <t>☐</t>
+    <t>R</t>
   </si>
   <si>
     <t>2</t>
@@ -614,7 +614,7 @@
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="37">
+  <fonts count="38">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -659,6 +659,11 @@
     <font>
       <sz val="10"/>
       <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Wingdings 2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1246,137 +1251,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1398,13 +1403,16 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1413,13 +1421,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1428,14 +1436,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1444,10 +1452,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1828,7 +1836,7 @@
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="28" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -1836,7 +1844,7 @@
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="28" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -1844,7 +1852,7 @@
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="27" t="s">
+      <c r="A6" s="28" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -1852,7 +1860,7 @@
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="27" t="s">
+      <c r="A7" s="28" t="s">
         <v>8</v>
       </c>
       <c r="C7" s="1" t="s">
@@ -1865,7 +1873,7 @@
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="27" t="s">
+      <c r="A10" s="28" t="s">
         <v>11</v>
       </c>
       <c r="C10" s="1" t="s">
@@ -1873,30 +1881,30 @@
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="27" t="s">
+      <c r="A11" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="28" t="s">
+      <c r="C11" s="29" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="27" t="s">
+      <c r="A12" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="29" t="e">
+      <c r="C12" s="30" t="e">
         <f>C11/C10</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E12" s="30" t="s">
+      <c r="E12" s="31" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="27" t="s">
+      <c r="A13" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="28" t="s">
+      <c r="C13" s="29" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1920,54 +1928,54 @@
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="15" t="s">
+      <c r="A17" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="B17" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="15" t="s">
+      <c r="C17" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="D17" s="15" t="s">
+      <c r="D17" s="16" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="15" t="s">
+      <c r="A18" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="D18" s="15" t="s">
+      <c r="D18" s="16" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="15" t="s">
+      <c r="A19" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C19" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="D19" s="15" t="s">
+      <c r="D19" s="16" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="15" t="s">
+      <c r="A20" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="B20" s="15"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
+      <c r="B20" s="16"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
     </row>
     <row r="22" ht="17.4" spans="1:4">
       <c r="A22" s="4" t="s">
@@ -1986,46 +1994,46 @@
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="15" t="s">
+      <c r="A24" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="31">
+      <c r="B24" s="32">
         <v>0</v>
       </c>
-      <c r="C24" s="14" t="s">
+      <c r="C24" s="15" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="15" t="s">
+      <c r="A25" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="31">
+      <c r="B25" s="32">
         <v>0</v>
       </c>
-      <c r="C25" s="14" t="s">
+      <c r="C25" s="15" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="15" t="s">
+      <c r="A26" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="B26" s="31">
+      <c r="B26" s="32">
         <v>0</v>
       </c>
-      <c r="C26" s="14" t="s">
+      <c r="C26" s="15" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="15" t="s">
+      <c r="A27" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="B27" s="31">
+      <c r="B27" s="32">
         <v>0</v>
       </c>
-      <c r="C27" s="14" t="s">
+      <c r="C27" s="15" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2066,7 +2074,7 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:8">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="26" t="s">
         <v>46</v>
       </c>
       <c r="B2" s="1"/>
@@ -2104,304 +2112,304 @@
       </c>
     </row>
     <row r="4" ht="100" customHeight="1" spans="1:8">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="D4" s="20" t="s">
+      <c r="D4" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="E4" s="20" t="s">
+      <c r="E4" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="F4" s="20" t="s">
+      <c r="F4" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="G4" s="20" t="s">
+      <c r="G4" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="H4" s="20" t="s">
+      <c r="H4" s="21" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="5" ht="100" customHeight="1" spans="1:8">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="D5" s="20" t="s">
+      <c r="D5" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="E5" s="20" t="s">
+      <c r="E5" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="F5" s="20" t="s">
+      <c r="F5" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="G5" s="20" t="s">
+      <c r="G5" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="H5" s="20" t="s">
+      <c r="H5" s="21" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="6" ht="80" customHeight="1" spans="1:8">
-      <c r="A6" s="32" t="s">
+      <c r="A6" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="D6" s="20" t="s">
+      <c r="D6" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="E6" s="20" t="s">
+      <c r="E6" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="F6" s="20" t="s">
+      <c r="F6" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="G6" s="20" t="s">
+      <c r="G6" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="H6" s="26" t="s">
+      <c r="H6" s="27" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="80" customHeight="1" spans="1:8">
-      <c r="A7" s="33" t="s">
+      <c r="A7" s="34" t="s">
         <v>78</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="D7" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="F7" s="15" t="s">
+      <c r="F7" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="G7" s="15" t="s">
+      <c r="G7" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="H7" s="15" t="s">
+      <c r="H7" s="16" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="80" customHeight="1" spans="1:8">
-      <c r="A8" s="34" t="s">
+      <c r="A8" s="35" t="s">
         <v>86</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="D8" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="E8" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="F8" s="15" t="s">
+      <c r="F8" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="G8" s="15" t="s">
+      <c r="G8" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="H8" s="15" t="s">
+      <c r="H8" s="16" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="80" customHeight="1" spans="1:8">
-      <c r="A9" s="15"/>
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15"/>
+      <c r="A9" s="16"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
     </row>
     <row r="10" ht="80" customHeight="1" spans="1:8">
-      <c r="A10" s="22"/>
-      <c r="B10" s="22"/>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="22"/>
-      <c r="H10" s="22"/>
+      <c r="A10" s="23"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="23"/>
+      <c r="G10" s="23"/>
+      <c r="H10" s="23"/>
     </row>
     <row r="11" ht="80" customHeight="1" spans="1:8">
-      <c r="A11" s="22"/>
-      <c r="B11" s="22"/>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="22"/>
-      <c r="G11" s="22"/>
-      <c r="H11" s="22"/>
+      <c r="A11" s="23"/>
+      <c r="B11" s="23"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="23"/>
+      <c r="F11" s="23"/>
+      <c r="G11" s="23"/>
+      <c r="H11" s="23"/>
     </row>
     <row r="12" ht="80" customHeight="1" spans="1:8">
-      <c r="A12" s="22"/>
-      <c r="B12" s="22"/>
-      <c r="C12" s="22"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="22"/>
-      <c r="H12" s="22"/>
+      <c r="A12" s="23"/>
+      <c r="B12" s="23"/>
+      <c r="C12" s="23"/>
+      <c r="D12" s="23"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="23"/>
+      <c r="G12" s="23"/>
+      <c r="H12" s="23"/>
     </row>
     <row r="13" ht="80" customHeight="1" spans="1:8">
-      <c r="A13" s="22"/>
-      <c r="B13" s="22"/>
-      <c r="C13" s="22"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="22"/>
-      <c r="H13" s="22"/>
+      <c r="A13" s="23"/>
+      <c r="B13" s="23"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="23"/>
+      <c r="H13" s="23"/>
     </row>
     <row r="14" ht="80" customHeight="1" spans="1:8">
-      <c r="A14" s="22"/>
-      <c r="B14" s="22"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="22"/>
-      <c r="H14" s="22"/>
+      <c r="A14" s="23"/>
+      <c r="B14" s="23"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="23"/>
+      <c r="G14" s="23"/>
+      <c r="H14" s="23"/>
     </row>
     <row r="15" ht="80" customHeight="1" spans="1:8">
-      <c r="A15" s="22"/>
-      <c r="B15" s="22"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="22"/>
-      <c r="H15" s="22"/>
+      <c r="A15" s="23"/>
+      <c r="B15" s="23"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23"/>
     </row>
     <row r="16" ht="80" customHeight="1" spans="1:8">
-      <c r="A16" s="22"/>
-      <c r="B16" s="22"/>
-      <c r="C16" s="22"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="22"/>
-      <c r="H16" s="22"/>
+      <c r="A16" s="23"/>
+      <c r="B16" s="23"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="23"/>
+      <c r="G16" s="23"/>
+      <c r="H16" s="23"/>
     </row>
     <row r="17" ht="80" customHeight="1" spans="1:8">
-      <c r="A17" s="22"/>
-      <c r="B17" s="22"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="22"/>
-      <c r="H17" s="22"/>
+      <c r="A17" s="23"/>
+      <c r="B17" s="23"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="23"/>
+      <c r="H17" s="23"/>
     </row>
     <row r="18" ht="80" customHeight="1" spans="1:8">
-      <c r="A18" s="22"/>
-      <c r="B18" s="22"/>
-      <c r="C18" s="22"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="22"/>
-      <c r="H18" s="22"/>
+      <c r="A18" s="23"/>
+      <c r="B18" s="23"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="23"/>
+      <c r="H18" s="23"/>
     </row>
     <row r="19" ht="80" customHeight="1" spans="1:8">
-      <c r="A19" s="22"/>
-      <c r="B19" s="22"/>
-      <c r="C19" s="22"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="22"/>
-      <c r="F19" s="22"/>
-      <c r="G19" s="22"/>
-      <c r="H19" s="22"/>
+      <c r="A19" s="23"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="23"/>
     </row>
     <row r="20" ht="80" customHeight="1" spans="1:8">
-      <c r="A20" s="22"/>
-      <c r="B20" s="22"/>
-      <c r="C20" s="22"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="22"/>
-      <c r="H20" s="22"/>
+      <c r="A20" s="23"/>
+      <c r="B20" s="23"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="23"/>
+      <c r="F20" s="23"/>
+      <c r="G20" s="23"/>
+      <c r="H20" s="23"/>
     </row>
     <row r="21" ht="80" customHeight="1" spans="1:8">
-      <c r="A21" s="22"/>
-      <c r="B21" s="22"/>
-      <c r="C21" s="22"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="22"/>
-      <c r="F21" s="22"/>
-      <c r="G21" s="22"/>
-      <c r="H21" s="22"/>
+      <c r="A21" s="23"/>
+      <c r="B21" s="23"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="23"/>
+      <c r="H21" s="23"/>
     </row>
     <row r="22" ht="80" customHeight="1" spans="1:8">
-      <c r="A22" s="22"/>
-      <c r="B22" s="22"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="22"/>
+      <c r="A22" s="23"/>
+      <c r="B22" s="23"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="23"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="23"/>
+      <c r="G22" s="23"/>
+      <c r="H22" s="23"/>
     </row>
     <row r="23" ht="80" customHeight="1" spans="1:8">
-      <c r="A23" s="22"/>
-      <c r="B23" s="22"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22"/>
-      <c r="G23" s="22"/>
-      <c r="H23" s="22"/>
+      <c r="A23" s="23"/>
+      <c r="B23" s="23"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="23"/>
+      <c r="H23" s="23"/>
     </row>
     <row r="24" ht="80" customHeight="1" spans="1:8">
-      <c r="A24" s="22"/>
-      <c r="B24" s="22"/>
-      <c r="C24" s="22"/>
-      <c r="D24" s="22"/>
-      <c r="E24" s="22"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="22"/>
-      <c r="H24" s="22"/>
+      <c r="A24" s="23"/>
+      <c r="B24" s="23"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="23"/>
+      <c r="E24" s="23"/>
+      <c r="F24" s="23"/>
+      <c r="G24" s="23"/>
+      <c r="H24" s="23"/>
     </row>
     <row r="25" ht="80" customHeight="1" spans="1:8">
-      <c r="A25" s="22"/>
-      <c r="B25" s="22"/>
-      <c r="C25" s="22"/>
-      <c r="D25" s="22"/>
-      <c r="E25" s="22"/>
-      <c r="F25" s="22"/>
-      <c r="G25" s="22"/>
-      <c r="H25" s="22"/>
+      <c r="A25" s="23"/>
+      <c r="B25" s="23"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="23"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="23"/>
+      <c r="G25" s="23"/>
+      <c r="H25" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2426,331 +2434,331 @@
   </cols>
   <sheetData>
     <row r="1" ht="21" spans="1:6">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="3" ht="40" customHeight="1" spans="1:6">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="F3" s="19" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="4" ht="60" customHeight="1" spans="1:6">
-      <c r="A4" s="32" t="s">
+      <c r="A4" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="D4" s="20" t="s">
+      <c r="D4" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="22" t="s">
         <v>105</v>
       </c>
-      <c r="F4" s="20" t="s">
+      <c r="F4" s="21" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="5" ht="100.8" spans="1:6">
-      <c r="A5" s="33" t="s">
+      <c r="A5" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="23" t="s">
         <v>107</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="23" t="s">
         <v>108</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="D5" s="23" t="s">
         <v>109</v>
       </c>
-      <c r="E5" s="22" t="s">
+      <c r="E5" s="23" t="s">
         <v>110</v>
       </c>
-      <c r="F5" s="22" t="s">
+      <c r="F5" s="23" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1" spans="1:6">
-      <c r="A6" s="33" t="s">
+      <c r="A6" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="23" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="D6" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="E6" s="22" t="s">
+      <c r="E6" s="23" t="s">
         <v>114</v>
       </c>
-      <c r="F6" s="22" t="s">
+      <c r="F6" s="23" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1" spans="1:6">
-      <c r="A7" s="33" t="s">
+      <c r="A7" s="34" t="s">
         <v>78</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="23" t="s">
         <v>116</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C7" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="D7" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="E7" s="22" t="s">
+      <c r="E7" s="23" t="s">
         <v>119</v>
       </c>
-      <c r="F7" s="22" t="s">
+      <c r="F7" s="23" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1" spans="1:6">
-      <c r="A8" s="33" t="s">
+      <c r="A8" s="34" t="s">
         <v>86</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="23" t="s">
         <v>121</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="C8" s="23" t="s">
         <v>122</v>
       </c>
-      <c r="D8" s="22" t="s">
+      <c r="D8" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="E8" s="22" t="s">
+      <c r="E8" s="23" t="s">
         <v>124</v>
       </c>
-      <c r="F8" s="22" t="s">
+      <c r="F8" s="23" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1" spans="1:6">
-      <c r="A9" s="22"/>
-      <c r="B9" s="22"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="22"/>
+      <c r="A9" s="23"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="23"/>
     </row>
     <row r="10" ht="60" customHeight="1" spans="1:6">
-      <c r="A10" s="22"/>
-      <c r="B10" s="22"/>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
+      <c r="A10" s="23"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="23"/>
     </row>
     <row r="11" ht="60" customHeight="1" spans="1:6">
-      <c r="A11" s="22"/>
-      <c r="B11" s="22"/>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="22"/>
+      <c r="A11" s="23"/>
+      <c r="B11" s="23"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="23"/>
+      <c r="F11" s="23"/>
     </row>
     <row r="12" ht="60" customHeight="1" spans="1:6">
-      <c r="A12" s="22"/>
-      <c r="B12" s="22"/>
-      <c r="C12" s="22"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="22"/>
+      <c r="A12" s="23"/>
+      <c r="B12" s="23"/>
+      <c r="C12" s="23"/>
+      <c r="D12" s="23"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="23"/>
     </row>
     <row r="13" ht="60" customHeight="1" spans="1:6">
-      <c r="A13" s="22"/>
-      <c r="B13" s="22"/>
-      <c r="C13" s="22"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22"/>
+      <c r="A13" s="23"/>
+      <c r="B13" s="23"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="23"/>
     </row>
     <row r="14" ht="60" customHeight="1" spans="1:6">
-      <c r="A14" s="22"/>
-      <c r="B14" s="22"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
+      <c r="A14" s="23"/>
+      <c r="B14" s="23"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="23"/>
     </row>
     <row r="15" ht="60" customHeight="1" spans="1:6">
-      <c r="A15" s="22"/>
-      <c r="B15" s="22"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
+      <c r="A15" s="23"/>
+      <c r="B15" s="23"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
     </row>
     <row r="16" ht="60" customHeight="1" spans="1:6">
-      <c r="A16" s="22"/>
-      <c r="B16" s="22"/>
-      <c r="C16" s="22"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
+      <c r="A16" s="23"/>
+      <c r="B16" s="23"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="23"/>
     </row>
     <row r="17" ht="60" customHeight="1" spans="1:6">
-      <c r="A17" s="22"/>
-      <c r="B17" s="22"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22"/>
+      <c r="A17" s="23"/>
+      <c r="B17" s="23"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="23"/>
     </row>
     <row r="18" ht="60" customHeight="1" spans="1:6">
-      <c r="A18" s="22"/>
-      <c r="B18" s="22"/>
-      <c r="C18" s="22"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22"/>
+      <c r="A18" s="23"/>
+      <c r="B18" s="23"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="23"/>
     </row>
     <row r="19" ht="60" customHeight="1" spans="1:6">
-      <c r="A19" s="22"/>
-      <c r="B19" s="22"/>
-      <c r="C19" s="22"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="22"/>
-      <c r="F19" s="22"/>
+      <c r="A19" s="23"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="23"/>
     </row>
     <row r="20" ht="60" customHeight="1" spans="1:6">
-      <c r="A20" s="22"/>
-      <c r="B20" s="22"/>
-      <c r="C20" s="22"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22"/>
+      <c r="A20" s="23"/>
+      <c r="B20" s="23"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="23"/>
+      <c r="F20" s="23"/>
     </row>
     <row r="21" ht="60" customHeight="1" spans="1:6">
-      <c r="A21" s="22"/>
-      <c r="B21" s="22"/>
-      <c r="C21" s="22"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="22"/>
-      <c r="F21" s="22"/>
+      <c r="A21" s="23"/>
+      <c r="B21" s="23"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="23"/>
     </row>
     <row r="22" ht="60" customHeight="1" spans="1:6">
-      <c r="A22" s="22"/>
-      <c r="B22" s="22"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
+      <c r="A22" s="23"/>
+      <c r="B22" s="23"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="23"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="23"/>
     </row>
     <row r="23" ht="60" customHeight="1" spans="1:6">
-      <c r="A23" s="22"/>
-      <c r="B23" s="22"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22"/>
+      <c r="A23" s="23"/>
+      <c r="B23" s="23"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="23"/>
     </row>
     <row r="24" ht="60" customHeight="1" spans="1:6">
-      <c r="A24" s="22"/>
-      <c r="B24" s="22"/>
-      <c r="C24" s="22"/>
-      <c r="D24" s="22"/>
-      <c r="E24" s="22"/>
-      <c r="F24" s="22"/>
+      <c r="A24" s="23"/>
+      <c r="B24" s="23"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="23"/>
+      <c r="E24" s="23"/>
+      <c r="F24" s="23"/>
     </row>
     <row r="30" ht="18" spans="1:6">
-      <c r="A30" s="23" t="s">
+      <c r="A30" s="24" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="31" spans="1:6">
-      <c r="A31" s="24" t="s">
+      <c r="A31" s="25" t="s">
         <v>127</v>
       </c>
-      <c r="B31" s="24" t="s">
+      <c r="B31" s="25" t="s">
         <v>128</v>
       </c>
-      <c r="C31" s="24" t="s">
+      <c r="C31" s="25" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="32" ht="28.8" spans="1:6">
-      <c r="A32" s="22" t="s">
+      <c r="A32" s="23" t="s">
         <v>130</v>
       </c>
-      <c r="B32" s="22" t="s">
+      <c r="B32" s="23" t="s">
         <v>131</v>
       </c>
-      <c r="C32" s="22" t="s">
+      <c r="C32" s="23" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="33" ht="28.8" spans="1:3">
-      <c r="A33" s="22" t="s">
+      <c r="A33" s="23" t="s">
         <v>133</v>
       </c>
-      <c r="B33" s="22" t="s">
+      <c r="B33" s="23" t="s">
         <v>134</v>
       </c>
-      <c r="C33" s="22" t="s">
+      <c r="C33" s="23" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="34" ht="28.8" spans="1:3">
-      <c r="A34" s="22" t="s">
+      <c r="A34" s="23" t="s">
         <v>136</v>
       </c>
-      <c r="B34" s="22" t="s">
+      <c r="B34" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="C34" s="22" t="s">
+      <c r="C34" s="23" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="35" ht="28.8" spans="1:3">
-      <c r="A35" s="22" t="s">
+      <c r="A35" s="23" t="s">
         <v>139</v>
       </c>
-      <c r="B35" s="22" t="s">
+      <c r="B35" s="23" t="s">
         <v>140</v>
       </c>
-      <c r="C35" s="22" t="s">
+      <c r="C35" s="23" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="36" ht="43.2" spans="1:3">
-      <c r="A36" s="22" t="s">
+      <c r="A36" s="23" t="s">
         <v>142</v>
       </c>
-      <c r="B36" s="22" t="s">
+      <c r="B36" s="23" t="s">
         <v>143</v>
       </c>
-      <c r="C36" s="22" t="s">
+      <c r="C36" s="23" t="s">
         <v>144</v>
       </c>
     </row>
@@ -2813,7 +2821,7 @@
       <c r="B6" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="9" t="s">
         <v>154</v>
       </c>
       <c r="D6" s="8"/>
@@ -2825,7 +2833,7 @@
       <c r="B7" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="9" t="s">
         <v>154</v>
       </c>
       <c r="D7" s="8"/>
@@ -2837,7 +2845,7 @@
       <c r="B8" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="9" t="s">
         <v>154</v>
       </c>
       <c r="D8" s="8"/>
@@ -2849,7 +2857,7 @@
       <c r="B9" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="9" t="s">
         <v>154</v>
       </c>
       <c r="D9" s="8"/>
@@ -2861,7 +2869,7 @@
       <c r="B10" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="9" t="s">
         <v>154</v>
       </c>
       <c r="D10" s="8"/>
@@ -2892,7 +2900,7 @@
       <c r="B14" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="9" t="s">
         <v>154</v>
       </c>
       <c r="D14" s="8"/>
@@ -2904,7 +2912,7 @@
       <c r="B15" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="9" t="s">
         <v>154</v>
       </c>
       <c r="D15" s="8"/>
@@ -2916,7 +2924,7 @@
       <c r="B16" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="9" t="s">
         <v>154</v>
       </c>
       <c r="D16" s="8"/>
@@ -2928,7 +2936,7 @@
       <c r="B17" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="9" t="s">
         <v>154</v>
       </c>
       <c r="D17" s="8"/>
@@ -2940,23 +2948,23 @@
       <c r="B18" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="9" t="s">
         <v>154</v>
       </c>
       <c r="D18" s="8"/>
     </row>
     <row r="20" ht="15.6" spans="1:4">
-      <c r="A20" s="9" t="s">
+      <c r="A20" s="10" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="10" t="s">
+      <c r="A21" s="11" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="10" t="s">
+      <c r="A22" s="11" t="s">
         <v>172</v>
       </c>
     </row>
@@ -2966,47 +2974,47 @@
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="11" t="s">
+      <c r="A26" s="12" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="27" ht="41.4" spans="1:4">
-      <c r="A27" s="12" t="s">
+      <c r="A27" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="B27" s="13" t="s">
+      <c r="B27" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="C27" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="D27" s="13" t="s">
+      <c r="D27" s="14" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="14" t="s">
+      <c r="A28" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="B28" s="15"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15"/>
+      <c r="B28" s="16"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="16"/>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="14" t="s">
+      <c r="A29" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="B29" s="15"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="15"/>
+      <c r="B29" s="16"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="16"/>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="14" t="s">
+      <c r="A30" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="B30" s="15"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="15"/>
+      <c r="B30" s="16"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="2">
